--- a/openspec/觀察題_11506.xlsx
+++ b/openspec/觀察題_11506.xlsx
@@ -620,7 +620,7 @@
         <v>廁所乾淨無髒污及垃圾桶無明顯滿溢</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>廁所髒污|垃圾桶明顯滿溢</v>
       </c>
       <c r="F10" t="str">
         <v>has</v>
@@ -643,7 +643,7 @@
         <v>落實填寫廁間清潔表；無堆放雜物（ex.紙箱、物流籃、資源回收物…等）</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>未落實填寫廁間清潔表|廁所堆放雜物</v>
       </c>
       <c r="F11" t="str">
         <v>has</v>
